--- a/code_notebooks/rekap_kombinasi_parameter_base_dan_meta.xlsx
+++ b/code_notebooks/rekap_kombinasi_parameter_base_dan_meta.xlsx
@@ -467,11 +467,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8412051800284454</v>
+        <v>0.8279420120929555</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -492,7 +492,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8313436634478629</v>
+        <v>0.8247075107452465</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
@@ -509,11 +509,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8308017067145744</v>
+        <v>0.8247060537626576</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
@@ -530,11 +530,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.826973575866457</v>
+        <v>0.8241684271872952</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -551,11 +551,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8231379594281009</v>
+        <v>0.8236235156989874</v>
       </c>
       <c r="E6" t="n">
         <v>5</v>
@@ -572,11 +572,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8214971180477582</v>
+        <v>0.8160763458876665</v>
       </c>
       <c r="E7" t="n">
         <v>6</v>
@@ -593,11 +593,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.8203982334007037</v>
+        <v>0.8149967217891747</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -614,11 +614,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.8182094468148813</v>
+        <v>0.8144620091789904</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -635,11 +635,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.8176629987274497</v>
+        <v>0.8133838420630873</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
@@ -656,11 +656,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8154532524889587</v>
+        <v>0.813378014132731</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
@@ -677,11 +677,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8132779399655663</v>
+        <v>0.8128360166096014</v>
       </c>
       <c r="E12" t="n">
         <v>11</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8121835466726551</v>
+        <v>0.8117636774240549</v>
       </c>
       <c r="E13" t="n">
         <v>12</v>
@@ -719,11 +719,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.8116415899393667</v>
+        <v>0.811218765935747</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -740,11 +740,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.8088943783217306</v>
+        <v>0.8106796823777958</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
@@ -761,11 +761,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.8083494273523467</v>
+        <v>0.8096029722444816</v>
       </c>
       <c r="E16" t="n">
         <v>15</v>
@@ -782,11 +782,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.8078014821468674</v>
+        <v>0.8090624317039412</v>
       </c>
       <c r="E17" t="n">
         <v>16</v>
@@ -803,11 +803,11 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.8077924994385807</v>
+        <v>0.8085233481459897</v>
       </c>
       <c r="E18" t="n">
         <v>17</v>
@@ -824,11 +824,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.8072550340594356</v>
+        <v>0.8085204341808115</v>
       </c>
       <c r="E19" t="n">
         <v>18</v>
@@ -845,11 +845,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.8072490455872445</v>
+        <v>0.8079900925183943</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -866,11 +866,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.8072475484691969</v>
+        <v>0.8069075544547243</v>
       </c>
       <c r="E21" t="n">
         <v>20</v>
@@ -887,14 +887,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.8061531551762856</v>
+        <v>0.8069075544547243</v>
       </c>
       <c r="E22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -908,11 +908,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.8056111984429972</v>
+        <v>0.8069002695417791</v>
       </c>
       <c r="E23" t="n">
         <v>22</v>
@@ -929,11 +929,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.8050677445916611</v>
+        <v>0.8042063087346106</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
@@ -950,11 +950,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.8050677445916611</v>
+        <v>0.8042063087346106</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
@@ -971,11 +971,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.8050617561194701</v>
+        <v>0.798272018649377</v>
       </c>
       <c r="E26" t="n">
         <v>25</v>
@@ -992,14 +992,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.8050617561194701</v>
+        <v>0.7971923945508851</v>
       </c>
       <c r="E27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -1013,11 +1013,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.8034194176210793</v>
+        <v>0.7966664238362352</v>
       </c>
       <c r="E28" t="n">
         <v>27</v>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.8034134291488882</v>
+        <v>0.7966664238362352</v>
       </c>
       <c r="E29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1055,11 +1055,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.8023235272101206</v>
+        <v>0.7966547679755227</v>
       </c>
       <c r="E30" t="n">
         <v>29</v>
@@ -1076,14 +1076,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.8017680964144024</v>
+        <v>0.7966547679755227</v>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
@@ -1097,11 +1097,11 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.7979504453926193</v>
+        <v>0.7961258832956946</v>
       </c>
       <c r="E32" t="n">
         <v>31</v>
@@ -1118,11 +1118,11 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.7974025001871399</v>
+        <v>0.7961156844175712</v>
       </c>
       <c r="E33" t="n">
         <v>32</v>
@@ -1139,11 +1139,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.7973860318886145</v>
+        <v>0.7950433452320246</v>
       </c>
       <c r="E34" t="n">
         <v>33</v>
@@ -1160,11 +1160,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.7968440751553261</v>
+        <v>0.7950418882494354</v>
       </c>
       <c r="E35" t="n">
         <v>34</v>
@@ -1181,11 +1181,11 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.7968425780372782</v>
+        <v>0.7928840970350406</v>
       </c>
       <c r="E36" t="n">
         <v>35</v>
@@ -1202,11 +1202,11 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.7968410809192304</v>
+        <v>0.7923450134770889</v>
       </c>
       <c r="E37" t="n">
         <v>36</v>
@@ -1223,11 +1223,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.7962946328317988</v>
+        <v>0.791268303343775</v>
       </c>
       <c r="E38" t="n">
         <v>37</v>
@@ -1244,11 +1244,11 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.796293135713751</v>
+        <v>0.7907277628032345</v>
       </c>
       <c r="E39" t="n">
         <v>38</v>
@@ -1265,11 +1265,11 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.7962916385957033</v>
+        <v>0.7842529321774604</v>
       </c>
       <c r="E40" t="n">
         <v>39</v>
@@ -1286,11 +1286,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.7957541732165581</v>
+        <v>0.7815604283528812</v>
       </c>
       <c r="E41" t="n">
         <v>40</v>
@@ -1307,11 +1307,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.7952017366569353</v>
+        <v>0.781557514387703</v>
       </c>
       <c r="E42" t="n">
         <v>41</v>
@@ -1328,11 +1328,11 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.7952002395388875</v>
+        <v>0.7794040941210751</v>
       </c>
       <c r="E43" t="n">
         <v>42</v>
@@ -1349,11 +1349,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.794102852009881</v>
+        <v>0.7793895242951847</v>
       </c>
       <c r="E44" t="n">
         <v>43</v>
@@ -1370,14 +1370,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.794102852009881</v>
+        <v>0.7793866103300064</v>
       </c>
       <c r="E45" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46">
@@ -1391,11 +1391,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.7919185567782019</v>
+        <v>0.7783259270051722</v>
       </c>
       <c r="E46" t="n">
         <v>45</v>
@@ -1412,11 +1412,11 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.7908286548394341</v>
+        <v>0.778318642092227</v>
       </c>
       <c r="E47" t="n">
         <v>46</v>
@@ -1433,14 +1433,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.7908286548394341</v>
+        <v>0.7777737306039192</v>
       </c>
       <c r="E48" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="49">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.7902702298076203</v>
+        <v>0.7777737306039192</v>
       </c>
       <c r="E49" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
@@ -1475,11 +1475,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.7897222846021409</v>
+        <v>0.777240474976324</v>
       </c>
       <c r="E50" t="n">
         <v>49</v>
@@ -1496,11 +1496,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.7891758365147092</v>
+        <v>0.777239017993735</v>
       </c>
       <c r="E51" t="n">
         <v>50</v>
@@ -1517,14 +1517,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.7891758365147092</v>
+        <v>0.7772361040285569</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="53">
@@ -1538,11 +1538,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.7886368740175163</v>
+        <v>0.7766999344357834</v>
       </c>
       <c r="E53" t="n">
         <v>52</v>
@@ -1559,11 +1559,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.7864435960775508</v>
+        <v>0.77508122677934</v>
       </c>
       <c r="E54" t="n">
         <v>53</v>
@@ -1580,11 +1580,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.7853477056665918</v>
+        <v>0.7745436002039776</v>
       </c>
       <c r="E55" t="n">
         <v>54</v>
@@ -1601,14 +1601,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.7853477056665918</v>
+        <v>0.7734654330880746</v>
       </c>
       <c r="E56" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57">
@@ -1622,14 +1622,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.7848012575791602</v>
+        <v>0.7734654330880746</v>
       </c>
       <c r="E57" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58">
@@ -1643,11 +1643,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.7782259151134067</v>
+        <v>0.772924892547534</v>
       </c>
       <c r="E58" t="n">
         <v>57</v>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.7771330189385433</v>
+        <v>0.7707700152983172</v>
       </c>
       <c r="E59" t="n">
         <v>58</v>
@@ -1685,11 +1685,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.7760341342914889</v>
+        <v>0.7707671013331391</v>
       </c>
       <c r="E60" t="n">
         <v>59</v>
@@ -1706,14 +1706,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.7760341342914889</v>
+        <v>0.7691483936766954</v>
       </c>
       <c r="E61" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
@@ -1727,11 +1727,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.7754757092596751</v>
+        <v>0.7686093101187441</v>
       </c>
       <c r="E62" t="n">
         <v>61</v>
@@ -1748,14 +1748,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.7754757092596751</v>
+        <v>0.7659182632767538</v>
       </c>
       <c r="E63" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -1769,11 +1769,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.7743917957930984</v>
+        <v>0.7659138923289867</v>
       </c>
       <c r="E64" t="n">
         <v>63</v>
@@ -1790,14 +1790,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.7743902986750506</v>
+        <v>0.7659138923289867</v>
       </c>
       <c r="E65" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66">
@@ -1811,11 +1811,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.7743783217306686</v>
+        <v>0.7621432213885043</v>
       </c>
       <c r="E66" t="n">
         <v>65</v>
@@ -1832,14 +1832,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.77164608129351</v>
+        <v>0.7621432213885043</v>
       </c>
       <c r="E67" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68">
@@ -1853,11 +1853,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.7689183322104948</v>
+        <v>0.7556756756756756</v>
       </c>
       <c r="E68" t="n">
         <v>67</v>
@@ -1874,14 +1874,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.7678164533273449</v>
+        <v>0.7556756756756756</v>
       </c>
       <c r="E69" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70">
@@ -1895,14 +1895,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.7678164533273449</v>
+        <v>0.7535062286005683</v>
       </c>
       <c r="E70" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71">
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.766726551388577</v>
+        <v>0.7529671450426167</v>
       </c>
       <c r="E71" t="n">
         <v>70</v>
@@ -1937,11 +1937,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.7656306609776181</v>
+        <v>0.7524280614846652</v>
       </c>
       <c r="E72" t="n">
         <v>71</v>
@@ -1958,11 +1958,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.7656276667415226</v>
+        <v>0.7491891891891892</v>
       </c>
       <c r="E73" t="n">
         <v>72</v>
@@ -1979,11 +1979,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.7612426079796393</v>
+        <v>0.7384002331172141</v>
       </c>
       <c r="E74" t="n">
         <v>73</v>
@@ -2000,14 +2000,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.7612426079796393</v>
+        <v>0.7362409849202303</v>
       </c>
       <c r="E75" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76">
@@ -2021,14 +2021,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.7612426079796393</v>
+        <v>0.7362409849202303</v>
       </c>
       <c r="E76" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77">
@@ -2042,11 +2042,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.7606916685380642</v>
+        <v>0.736235156989874</v>
       </c>
       <c r="E77" t="n">
         <v>76</v>
@@ -2063,14 +2063,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.7601497118047758</v>
+        <v>0.736235156989874</v>
       </c>
       <c r="E78" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79">
@@ -2084,14 +2084,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.7601497118047758</v>
+        <v>0.736235156989874</v>
       </c>
       <c r="E79" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="80">
@@ -2105,14 +2105,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.7601497118047758</v>
+        <v>0.736235156989874</v>
       </c>
       <c r="E80" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81">
@@ -2126,14 +2126,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.7601497118047758</v>
+        <v>0.7351657317695054</v>
       </c>
       <c r="E81" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82">
@@ -2147,11 +2147,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.7601407290964892</v>
+        <v>0.7351584468565602</v>
       </c>
       <c r="E82" t="n">
         <v>81</v>
@@ -2168,11 +2168,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.7601407290964892</v>
+        <v>0.7351584468565602</v>
       </c>
       <c r="E83" t="n">
         <v>81</v>
@@ -2189,11 +2189,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.7595987723632007</v>
+        <v>0.7351569898739709</v>
       </c>
       <c r="E84" t="n">
         <v>83</v>
@@ -2210,11 +2210,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.7595987723632007</v>
+        <v>0.7351569898739709</v>
       </c>
       <c r="E85" t="n">
         <v>83</v>
@@ -2231,11 +2231,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.7595972752451531</v>
+        <v>0.7346281051941429</v>
       </c>
       <c r="E86" t="n">
         <v>85</v>
@@ -2252,14 +2252,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.7595972752451531</v>
+        <v>0.7340890216361914</v>
       </c>
       <c r="E87" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="88">
@@ -2273,11 +2273,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.7585028819522419</v>
+        <v>0.7340802797406571</v>
       </c>
       <c r="E88" t="n">
         <v>87</v>
@@ -2294,14 +2294,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.7579594281009058</v>
+        <v>0.7340802797406571</v>
       </c>
       <c r="E89" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90">
@@ -2315,14 +2315,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.7568650348079945</v>
+        <v>0.7340802797406571</v>
       </c>
       <c r="E90" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91">
@@ -2336,14 +2336,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.7568650348079945</v>
+        <v>0.7340802797406571</v>
       </c>
       <c r="E91" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92">
@@ -2357,11 +2357,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.7568635376899469</v>
+        <v>0.7335397392001166</v>
       </c>
       <c r="E92" t="n">
         <v>91</v>
@@ -2378,14 +2378,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.7568635376899469</v>
+        <v>0.7324586581190355</v>
       </c>
       <c r="E93" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94">
@@ -2399,14 +2399,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.7563125982483718</v>
+        <v>0.7324586581190355</v>
       </c>
       <c r="E94" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95">
@@ -2420,14 +2420,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.7563125982483718</v>
+        <v>0.7324586581190354</v>
       </c>
       <c r="E95" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96">
@@ -2441,14 +2441,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.7563125982483718</v>
+        <v>0.7324586581190354</v>
       </c>
       <c r="E96" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97">
@@ -2462,14 +2462,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.7563125982483718</v>
+        <v>0.7313834049683107</v>
       </c>
       <c r="E97" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98">
@@ -2483,11 +2483,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.755767647278988</v>
+        <v>0.7308457783929482</v>
       </c>
       <c r="E98" t="n">
         <v>97</v>
@@ -2504,14 +2504,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.755767647278988</v>
+        <v>0.7308443214103592</v>
       </c>
       <c r="E99" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="100">
@@ -2525,14 +2525,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.7557676472789879</v>
+        <v>0.7308443214103592</v>
       </c>
       <c r="E100" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101">
@@ -2546,14 +2546,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.7557676472789879</v>
+        <v>0.7308443214103592</v>
       </c>
       <c r="E101" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102">
@@ -2567,11 +2567,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.7552197020735084</v>
+        <v>0.7308414074451811</v>
       </c>
       <c r="E102" t="n">
         <v>101</v>
@@ -2588,11 +2588,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.7552197020735084</v>
+        <v>0.7308414074451811</v>
       </c>
       <c r="E103" t="n">
         <v>101</v>
@@ -2609,11 +2609,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.7552137136013176</v>
+        <v>0.7303110657827638</v>
       </c>
       <c r="E104" t="n">
         <v>103</v>
@@ -2630,14 +2630,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.7552137136013176</v>
+        <v>0.7303081518175858</v>
       </c>
       <c r="E105" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106">
@@ -2651,14 +2651,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.7552137136013176</v>
+        <v>0.7303066948349967</v>
       </c>
       <c r="E106" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="107">
@@ -2672,14 +2672,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.7541253087805974</v>
+        <v>0.7303066948349967</v>
       </c>
       <c r="E107" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="108">
@@ -2693,11 +2693,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.7541238116625496</v>
+        <v>0.7297661542944561</v>
       </c>
       <c r="E108" t="n">
         <v>107</v>
@@ -2714,14 +2714,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.7535743693390223</v>
+        <v>0.7297661542944561</v>
       </c>
       <c r="E109" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110">
@@ -2735,14 +2735,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.7535743693390223</v>
+        <v>0.7292299847016828</v>
       </c>
       <c r="E110" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="111">
@@ -2756,14 +2756,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.7513885769892956</v>
+        <v>0.7292299847016828</v>
       </c>
       <c r="E111" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="112">
@@ -2777,14 +2777,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.7513885769892956</v>
+        <v>0.7292299847016828</v>
       </c>
       <c r="E112" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113">
@@ -2798,14 +2798,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.7513885769892956</v>
+        <v>0.7292299847016828</v>
       </c>
       <c r="E113" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="114">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.7513885769892956</v>
+        <v>0.7292299847016828</v>
       </c>
       <c r="E114" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="115">
@@ -2840,14 +2840,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.7513885769892956</v>
+        <v>0.7292299847016828</v>
       </c>
       <c r="E115" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="116">
@@ -2861,14 +2861,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.7513885769892956</v>
+        <v>0.7292299847016828</v>
       </c>
       <c r="E116" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="117">
@@ -2882,14 +2882,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.7508436260199117</v>
+        <v>0.7292299847016828</v>
       </c>
       <c r="E117" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="118">
@@ -2903,14 +2903,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.7508436260199117</v>
+        <v>0.7292299847016828</v>
       </c>
       <c r="E118" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="119">
@@ -2924,14 +2924,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.7508436260199117</v>
+        <v>0.7286967290740874</v>
       </c>
       <c r="E119" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120">
@@ -2945,11 +2945,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.74919529904933</v>
+        <v>0.7286894441611421</v>
       </c>
       <c r="E120" t="n">
         <v>119</v>
@@ -2966,14 +2966,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.74919529904933</v>
+        <v>0.728153274568369</v>
       </c>
       <c r="E121" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122">
@@ -2987,14 +2987,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.74919529904933</v>
+        <v>0.728153274568369</v>
       </c>
       <c r="E122" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123">
@@ -3008,14 +3008,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.74919529904933</v>
+        <v>0.7276141910104175</v>
       </c>
       <c r="E123" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="124">
@@ -3029,14 +3029,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.7480994086383711</v>
+        <v>0.7276141910104175</v>
       </c>
       <c r="E124" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.7480979115203235</v>
+        <v>0.7276141910104175</v>
       </c>
       <c r="E125" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="126">
@@ -3071,11 +3071,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.7480964144022756</v>
+        <v>0.727076564435055</v>
       </c>
       <c r="E126" t="n">
         <v>125</v>
@@ -3092,14 +3092,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.7475514634328917</v>
+        <v>0.727076564435055</v>
       </c>
       <c r="E127" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="128">
@@ -3113,14 +3113,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.7475514634328917</v>
+        <v>0.7270736504698769</v>
       </c>
       <c r="E128" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="129">
@@ -3134,14 +3134,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.7475514634328917</v>
+        <v>0.7270736504698769</v>
       </c>
       <c r="E129" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="130">
@@ -3155,14 +3155,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.7475514634328917</v>
+        <v>0.7265331099293364</v>
       </c>
       <c r="E130" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="131">
@@ -3176,14 +3176,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.7475514634328917</v>
+        <v>0.7265316529467473</v>
       </c>
       <c r="E131" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="132">
@@ -3197,14 +3197,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.7470065124635077</v>
+        <v>0.7265316529467473</v>
       </c>
       <c r="E132" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="133">
@@ -3218,14 +3218,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.7470065124635077</v>
+        <v>0.7259940263713849</v>
       </c>
       <c r="E133" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134">
@@ -3239,14 +3239,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.742085485440527</v>
+        <v>0.7259940263713849</v>
       </c>
       <c r="E134" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="135">
@@ -3260,14 +3260,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.742085485440527</v>
+        <v>0.7259911124062066</v>
       </c>
       <c r="E135" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="136">
@@ -3281,14 +3281,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.7415270604087133</v>
+        <v>0.7259911124062066</v>
       </c>
       <c r="E136" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137">
@@ -3302,14 +3302,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.7415270604087133</v>
+        <v>0.7254520288482553</v>
       </c>
       <c r="E137" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="138">
@@ -3323,14 +3323,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.740977618085186</v>
+        <v>0.7254520288482553</v>
       </c>
       <c r="E138" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139">
@@ -3344,14 +3344,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.7393517478853207</v>
+        <v>0.7254520288482553</v>
       </c>
       <c r="E139" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="140">
@@ -3365,11 +3365,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.7393397709409387</v>
+        <v>0.7249144022728928</v>
       </c>
       <c r="E140" t="n">
         <v>139</v>
@@ -3386,11 +3386,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.7360595852983007</v>
+        <v>0.7232927806512712</v>
       </c>
       <c r="E141" t="n">
         <v>140</v>
@@ -3411,7 +3411,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.7355026573845347</v>
+        <v>0.7227566110584979</v>
       </c>
       <c r="E142" t="n">
         <v>141</v>
@@ -3432,10 +3432,10 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.7355026573845347</v>
+        <v>0.7222160705179573</v>
       </c>
       <c r="E143" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="144">
@@ -3449,11 +3449,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.7322179803877537</v>
+        <v>0.7222116995701902</v>
       </c>
       <c r="E144" t="n">
         <v>143</v>
@@ -3470,14 +3470,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.7311280784489856</v>
+        <v>0.7222116995701902</v>
       </c>
       <c r="E145" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="146">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.9479766449584549</v>
+        <v>0.943914912216799</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
@@ -3512,11 +3512,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.9468777603114006</v>
+        <v>0.94391345523421</v>
       </c>
       <c r="E147" t="n">
         <v>2</v>
@@ -3533,14 +3533,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.9452324275769144</v>
+        <v>0.94391345523421</v>
       </c>
       <c r="E148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -3554,11 +3554,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.9446919679616738</v>
+        <v>0.9439105412690317</v>
       </c>
       <c r="E149" t="n">
         <v>4</v>
@@ -3575,11 +3575,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.9446919679616738</v>
+        <v>0.9439105412690317</v>
       </c>
       <c r="E150" t="n">
         <v>4</v>
@@ -3596,11 +3596,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.943596077550715</v>
+        <v>0.9428294601879508</v>
       </c>
       <c r="E151" t="n">
         <v>6</v>
@@ -3617,14 +3617,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.9403099034358859</v>
+        <v>0.9428294601879508</v>
       </c>
       <c r="E152" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153">
@@ -3638,14 +3638,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.9403099034358859</v>
+        <v>0.9412151234792743</v>
       </c>
       <c r="E153" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -3659,14 +3659,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.9397694438206454</v>
+        <v>0.9412151234792743</v>
       </c>
       <c r="E154" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155">
@@ -3680,14 +3680,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.9397694438206454</v>
+        <v>0.94068041086909</v>
       </c>
       <c r="E155" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156">
@@ -3701,11 +3701,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.939220001497118</v>
+        <v>0.9401398703285496</v>
       </c>
       <c r="E156" t="n">
         <v>11</v>
@@ -3722,11 +3722,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.939220001497118</v>
+        <v>0.9401398703285496</v>
       </c>
       <c r="E157" t="n">
         <v>11</v>
@@ -3743,14 +3743,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.9381241110861591</v>
+        <v>0.9401398703285496</v>
       </c>
       <c r="E158" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159">
@@ -3764,11 +3764,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.9337435436784191</v>
+        <v>0.9390558752822905</v>
       </c>
       <c r="E159" t="n">
         <v>14</v>
@@ -3785,14 +3785,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.9332000898270829</v>
+        <v>0.9390558752822905</v>
       </c>
       <c r="E160" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="161">
@@ -3806,11 +3806,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.9310098061232128</v>
+        <v>0.9379791651489764</v>
       </c>
       <c r="E161" t="n">
         <v>16</v>
@@ -3827,11 +3827,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.9310038176510218</v>
+        <v>0.9363619144751221</v>
       </c>
       <c r="E162" t="n">
         <v>17</v>
@@ -3848,14 +3848,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.9310038176510218</v>
+        <v>0.93528229037663</v>
       </c>
       <c r="E163" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="164">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.9277221348903361</v>
+        <v>0.93528229037663</v>
       </c>
       <c r="E164" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="165">
@@ -3890,14 +3890,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.9277221348903361</v>
+        <v>0.9352808333940409</v>
       </c>
       <c r="E165" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166">
@@ -3911,11 +3911,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.9271726925668089</v>
+        <v>0.9347446638012675</v>
       </c>
       <c r="E166" t="n">
         <v>21</v>
@@ -3932,14 +3932,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.9271726925668089</v>
+        <v>0.9347432068186785</v>
       </c>
       <c r="E167" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="168">
@@ -3953,14 +3953,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.9266277415974251</v>
+        <v>0.9347432068186785</v>
       </c>
       <c r="E168" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="169">
@@ -3974,14 +3974,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.9266277415974251</v>
+        <v>0.9315057915057915</v>
       </c>
       <c r="E169" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="170">
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.8346178606183097</v>
+        <v>0.8500604647774459</v>
       </c>
       <c r="E170" t="n">
         <v>25</v>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.8346178606183097</v>
+        <v>0.8500604647774459</v>
       </c>
       <c r="E171" t="n">
         <v>25</v>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.8340684182947825</v>
+        <v>0.8398120492460116</v>
       </c>
       <c r="E172" t="n">
         <v>27</v>
@@ -4062,7 +4062,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.8225780372782394</v>
+        <v>0.8300939753769943</v>
       </c>
       <c r="E173" t="n">
         <v>28</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.8154652294333408</v>
+        <v>0.8284854665986743</v>
       </c>
       <c r="E174" t="n">
         <v>29</v>
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.8154652294333408</v>
+        <v>0.8284854665986743</v>
       </c>
       <c r="E175" t="n">
         <v>29</v>
@@ -4121,11 +4121,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.8083404446440602</v>
+        <v>0.8203861003861004</v>
       </c>
       <c r="E176" t="n">
         <v>31</v>
@@ -4142,14 +4142,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.8083404446440602</v>
+        <v>0.81661251548044</v>
       </c>
       <c r="E177" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="178">
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.8083404446440602</v>
+        <v>0.81661251548044</v>
       </c>
       <c r="E178" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="179">
@@ -4184,11 +4184,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.7968425780372782</v>
+        <v>0.8117549355285204</v>
       </c>
       <c r="E179" t="n">
         <v>34</v>
@@ -4205,14 +4205,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.7968425780372782</v>
+        <v>0.8096015152618927</v>
       </c>
       <c r="E180" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="181">
@@ -4226,14 +4226,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.7962961299498466</v>
+        <v>0.8096015152618927</v>
       </c>
       <c r="E181" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="182">
@@ -4247,14 +4247,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0.7962961299498466</v>
+        <v>0.8020485175202158</v>
       </c>
       <c r="E182" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="183">
@@ -4268,14 +4268,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.7924650048656335</v>
+        <v>0.8020485175202158</v>
       </c>
       <c r="E183" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="184">
@@ -4289,14 +4289,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0.7924650048656335</v>
+        <v>0.7869439790194507</v>
       </c>
       <c r="E184" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="185">
@@ -4310,11 +4310,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0.7919065798338198</v>
+        <v>0.7853252713630072</v>
       </c>
       <c r="E185" t="n">
         <v>40</v>
@@ -4331,11 +4331,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0.7919065798338198</v>
+        <v>0.7853252713630072</v>
       </c>
       <c r="E186" t="n">
         <v>40</v>
@@ -4352,11 +4352,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.7902747211617637</v>
+        <v>0.7837109346543308</v>
       </c>
       <c r="E187" t="n">
         <v>42</v>
@@ -4373,14 +4373,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.7902747211617637</v>
+        <v>0.7810111459168063</v>
       </c>
       <c r="E188" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="189">
@@ -4394,11 +4394,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.7897222846021408</v>
+        <v>0.7788518977198222</v>
       </c>
       <c r="E189" t="n">
         <v>44</v>
@@ -4415,14 +4415,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.7886204057189909</v>
+        <v>0.7788518977198222</v>
       </c>
       <c r="E190" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="191">
@@ -4436,11 +4436,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.7875349951343663</v>
+        <v>0.7761579369126539</v>
       </c>
       <c r="E191" t="n">
         <v>46</v>
@@ -4457,11 +4457,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.7869855528108392</v>
+        <v>0.7756203103372915</v>
       </c>
       <c r="E192" t="n">
         <v>47</v>
@@ -4478,14 +4478,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.7853447114304963</v>
+        <v>0.7756203103372915</v>
       </c>
       <c r="E193" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="194">
@@ -4499,11 +4499,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.7574189684856651</v>
+        <v>0.7481183069862316</v>
       </c>
       <c r="E194" t="n">
         <v>1</v>
@@ -4520,11 +4520,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.7486563365521371</v>
+        <v>0.7427158155460042</v>
       </c>
       <c r="E195" t="n">
         <v>2</v>
@@ -4541,11 +4541,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0.747561943259226</v>
+        <v>0.7340861076710133</v>
       </c>
       <c r="E196" t="n">
         <v>3</v>
@@ -4562,11 +4562,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.7464690470843627</v>
+        <v>0.7308559772710715</v>
       </c>
       <c r="E197" t="n">
         <v>4</v>
@@ -4583,11 +4583,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0.7459181076427877</v>
+        <v>0.730315436730531</v>
       </c>
       <c r="E198" t="n">
         <v>5</v>
@@ -4604,11 +4604,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.7459166105247399</v>
+        <v>0.7292328986668609</v>
       </c>
       <c r="E199" t="n">
         <v>6</v>
@@ -4625,11 +4625,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.745371659555356</v>
+        <v>0.7286952720914985</v>
       </c>
       <c r="E200" t="n">
         <v>7</v>
@@ -4646,11 +4646,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0.7453716595553559</v>
+        <v>0.7286923581263205</v>
       </c>
       <c r="E201" t="n">
         <v>8</v>
@@ -4667,11 +4667,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.7453701624373082</v>
+        <v>0.7286909011437313</v>
       </c>
       <c r="E202" t="n">
         <v>9</v>
@@ -4688,11 +4688,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.7453701624373081</v>
+        <v>0.7276141910104175</v>
       </c>
       <c r="E203" t="n">
         <v>10</v>
@@ -4709,14 +4709,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.7453701624373081</v>
+        <v>0.7276112770452393</v>
       </c>
       <c r="E204" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205">
@@ -4730,11 +4730,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.7448237143498766</v>
+        <v>0.7270736504698768</v>
       </c>
       <c r="E205" t="n">
         <v>12</v>
@@ -4751,11 +4751,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7265331099293363</v>
       </c>
       <c r="E206" t="n">
         <v>13</v>
@@ -4772,11 +4772,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7265331099293363</v>
       </c>
       <c r="E207" t="n">
         <v>13</v>
@@ -4793,11 +4793,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7265331099293363</v>
       </c>
       <c r="E208" t="n">
         <v>13</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7265331099293363</v>
       </c>
       <c r="E209" t="n">
         <v>13</v>
@@ -4835,11 +4835,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7265331099293363</v>
       </c>
       <c r="E210" t="n">
         <v>13</v>
@@ -4856,11 +4856,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7265331099293363</v>
       </c>
       <c r="E211" t="n">
         <v>13</v>
@@ -4877,11 +4877,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7265331099293363</v>
       </c>
       <c r="E212" t="n">
         <v>13</v>
@@ -4898,11 +4898,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7265331099293363</v>
       </c>
       <c r="E213" t="n">
         <v>13</v>
@@ -4919,11 +4919,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7265331099293363</v>
       </c>
       <c r="E214" t="n">
         <v>13</v>
@@ -4940,11 +4940,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7265331099293363</v>
       </c>
       <c r="E215" t="n">
         <v>13</v>
@@ -4961,14 +4961,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7259998543017411</v>
       </c>
       <c r="E216" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217">
@@ -4982,14 +4982,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7259983973191521</v>
       </c>
       <c r="E217" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="218">
@@ -5003,14 +5003,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7259940263713848</v>
       </c>
       <c r="E218" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="219">
@@ -5024,14 +5024,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0.7448237143498765</v>
+        <v>0.7259940263713848</v>
       </c>
       <c r="E219" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="220">
@@ -5045,14 +5045,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.7448222172318288</v>
+        <v>0.7259940263713848</v>
       </c>
       <c r="E220" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="221">
@@ -5066,14 +5066,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>0.7448222172318288</v>
+        <v>0.7254549428134334</v>
       </c>
       <c r="E221" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="222">
@@ -5087,14 +5087,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.7448222172318288</v>
+        <v>0.7254549428134334</v>
       </c>
       <c r="E222" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="223">
@@ -5108,14 +5108,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.7442757691443971</v>
+        <v>0.7254549428134334</v>
       </c>
       <c r="E223" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="224">
@@ -5129,14 +5129,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0.7442682835541583</v>
+        <v>0.7254549428134334</v>
       </c>
       <c r="E224" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="225">
@@ -5150,14 +5150,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.7431768844973426</v>
+        <v>0.7254549428134334</v>
       </c>
       <c r="E225" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="226">
@@ -5171,11 +5171,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.7415345459989521</v>
+        <v>0.7254534858308442</v>
       </c>
       <c r="E226" t="n">
         <v>33</v>
@@ -5192,11 +5192,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.7415315517628565</v>
+        <v>0.7249129452903038</v>
       </c>
       <c r="E227" t="n">
         <v>34</v>
@@ -5213,14 +5213,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.7393382738228909</v>
+        <v>0.7249129452903038</v>
       </c>
       <c r="E228" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="229">
@@ -5234,11 +5234,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0.7387933228535071</v>
+        <v>0.7238376921395788</v>
       </c>
       <c r="E229" t="n">
         <v>36</v>
@@ -5255,11 +5255,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0.7382513661202187</v>
+        <v>0.721682814890362</v>
       </c>
       <c r="E230" t="n">
         <v>37</v>
@@ -5280,7 +5280,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>0.7371449958829253</v>
+        <v>0.7216784439425948</v>
       </c>
       <c r="E231" t="n">
         <v>38</v>
@@ -5297,11 +5297,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0.7349517179429599</v>
+        <v>0.7189932250309609</v>
       </c>
       <c r="E232" t="n">
         <v>39</v>
@@ -5318,11 +5318,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>0.7300321880380267</v>
+        <v>0.7184410286297078</v>
       </c>
       <c r="E233" t="n">
         <v>40</v>
@@ -5339,11 +5339,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0.7289437832173067</v>
+        <v>0.7173686894441612</v>
       </c>
       <c r="E234" t="n">
         <v>41</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.7256650946927166</v>
+        <v>0.7168281489036207</v>
       </c>
       <c r="E235" t="n">
         <v>42</v>
@@ -5381,11 +5381,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0.7251096638969983</v>
+        <v>0.715206527281999</v>
       </c>
       <c r="E236" t="n">
         <v>43</v>
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0.7190972378172018</v>
+        <v>0.7108953158009762</v>
       </c>
       <c r="E237" t="n">
         <v>44</v>
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0.7092237442922374</v>
+        <v>0.7038945144605522</v>
       </c>
       <c r="E238" t="n">
         <v>45</v>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>0.6681727674227114</v>
+        <v>0.6952604356377942</v>
       </c>
       <c r="E239" t="n">
         <v>46</v>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0.6319365221947751</v>
+        <v>0.6397056895170102</v>
       </c>
       <c r="E240" t="n">
         <v>47</v>
@@ -5486,11 +5486,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.532252414102852</v>
+        <v>0.6375697530414511</v>
       </c>
       <c r="E241" t="n">
         <v>48</v>
@@ -5507,11 +5507,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0.5279676622501686</v>
+        <v>0.5750273184235448</v>
       </c>
       <c r="E242" t="n">
         <v>49</v>
@@ -5528,11 +5528,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0.5202964293734561</v>
+        <v>0.5636832519851389</v>
       </c>
       <c r="E243" t="n">
         <v>50</v>
@@ -5549,11 +5549,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0.5016198817276744</v>
+        <v>0.5156436220587164</v>
       </c>
       <c r="E244" t="n">
         <v>51</v>
@@ -5570,11 +5570,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0001), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0.5000224567707164</v>
+        <v>0.500001456982589</v>
       </c>
       <c r="E245" t="n">
         <v>52</v>
@@ -5591,11 +5591,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>0.5000224567707164</v>
+        <v>0.500001456982589</v>
       </c>
       <c r="E246" t="n">
         <v>52</v>
@@ -5612,11 +5612,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>0.5000224567707164</v>
+        <v>0.500001456982589</v>
       </c>
       <c r="E247" t="n">
         <v>52</v>
@@ -5633,14 +5633,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0001), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>0.5000224567707164</v>
+        <v>0.499998543017411</v>
       </c>
       <c r="E248" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="249">
@@ -5654,14 +5654,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D249" t="n">
-        <v>0.5000224567707164</v>
+        <v>0.499998543017411</v>
       </c>
       <c r="E249" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="250">
@@ -5675,14 +5675,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D250" t="n">
-        <v>0.4999775432292837</v>
+        <v>0.499998543017411</v>
       </c>
       <c r="E250" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="251">
@@ -5696,14 +5696,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D251" t="n">
-        <v>0.4999775432292837</v>
+        <v>0.499998543017411</v>
       </c>
       <c r="E251" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="252">
@@ -5717,14 +5717,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D252" t="n">
-        <v>0.4841320458118124</v>
+        <v>0.499998543017411</v>
       </c>
       <c r="E252" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="253">
@@ -5738,11 +5738,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D253" t="n">
-        <v>0.4742690321131821</v>
+        <v>0.4892168718583813</v>
       </c>
       <c r="E253" t="n">
         <v>60</v>
@@ -5763,7 +5763,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>0.9189565087207127</v>
+        <v>0.9185590442194217</v>
       </c>
       <c r="E254" t="n">
         <v>1</v>
@@ -5784,7 +5784,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>0.8691234373830377</v>
+        <v>0.8657011728709841</v>
       </c>
       <c r="E255" t="n">
         <v>2</v>
@@ -5805,7 +5805,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>0.830247773036904</v>
+        <v>0.8306374298827131</v>
       </c>
       <c r="E256" t="n">
         <v>3</v>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>0.8088958754397785</v>
+        <v>0.7988125591899177</v>
       </c>
       <c r="E257" t="n">
         <v>4</v>
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>0.7990268732689573</v>
+        <v>0.7923420995119108</v>
       </c>
       <c r="E258" t="n">
         <v>5</v>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0.7902747211617636</v>
+        <v>0.772919064617178</v>
       </c>
       <c r="E259" t="n">
         <v>6</v>
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>0.7765865708511116</v>
+        <v>0.7610592263422452</v>
       </c>
       <c r="E260" t="n">
         <v>7</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>0.7678299273897746</v>
+        <v>0.7567349020179208</v>
       </c>
       <c r="E261" t="n">
         <v>8</v>
@@ -5927,11 +5927,11 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'linear'}</t>
+          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0.7574144771315219</v>
+        <v>0.7270707365046987</v>
       </c>
       <c r="E262" t="n">
         <v>9</v>
@@ -5948,11 +5948,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'linear'}</t>
+          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>0.7574144771315219</v>
+        <v>0.7270707365046987</v>
       </c>
       <c r="E263" t="n">
         <v>9</v>
@@ -5973,10 +5973,10 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0.7568650348079947</v>
+        <v>0.7270707365046987</v>
       </c>
       <c r="E264" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="265">
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>0.7568650348079947</v>
+        <v>0.7270707365046987</v>
       </c>
       <c r="E265" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="266">
@@ -6011,11 +6011,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'linear'}</t>
+          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0.7563170896025152</v>
+        <v>0.7254520288482553</v>
       </c>
       <c r="E266" t="n">
         <v>13</v>
@@ -6032,11 +6032,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'linear'}</t>
+          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0.7563170896025152</v>
+        <v>0.7254520288482553</v>
       </c>
       <c r="E267" t="n">
         <v>13</v>
@@ -6053,11 +6053,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'linear'}</t>
+          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>0.7491952990493299</v>
+        <v>0.722759525023676</v>
       </c>
       <c r="E268" t="n">
         <v>15</v>
@@ -6074,14 +6074,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'linear'}</t>
+          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>0.7491952990493299</v>
+        <v>0.7216784439425948</v>
       </c>
       <c r="E269" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="270">
@@ -6095,14 +6095,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>0.7366060333857325</v>
+        <v>0.7216784439425948</v>
       </c>
       <c r="E270" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="271">
@@ -6116,11 +6116,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'linear'}</t>
+          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>0.7289407889812113</v>
+        <v>0.7216740729948278</v>
       </c>
       <c r="E271" t="n">
         <v>18</v>
@@ -6137,11 +6137,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'linear'}</t>
+          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0.7289407889812113</v>
+        <v>0.7216740729948278</v>
       </c>
       <c r="E272" t="n">
         <v>18</v>
@@ -6162,7 +6162,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0.724560221573471</v>
+        <v>0.7173701464267502</v>
       </c>
       <c r="E273" t="n">
         <v>20</v>
@@ -6220,11 +6220,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9490710382513662</v>
+        <v>0.9455350768558315</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -6241,11 +6241,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9490710382513662</v>
+        <v>0.9455350768558315</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -6262,11 +6262,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9490710382513662</v>
+        <v>0.9455350768558315</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -6283,11 +6283,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9485260872819822</v>
+        <v>0.9455336198732425</v>
       </c>
       <c r="E5" t="n">
         <v>4</v>
@@ -6304,11 +6304,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9485260872819822</v>
+        <v>0.9455336198732425</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
@@ -6325,14 +6325,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9485230930458867</v>
+        <v>0.9455336198732425</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -6346,14 +6346,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9485230930458867</v>
+        <v>0.9455336198732425</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6367,14 +6367,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9485230930458867</v>
+        <v>0.9455292489254752</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -6388,14 +6388,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9485215959278388</v>
+        <v>0.9455292489254752</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -6409,14 +6409,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9485215959278388</v>
+        <v>0.9449959932978802</v>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -6430,14 +6430,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9485215959278388</v>
+        <v>0.9449959932978802</v>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -6451,14 +6451,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9485215959278388</v>
+        <v>0.9449959932978802</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -6472,14 +6472,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.9485215959278388</v>
+        <v>0.94499599329788</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -6493,14 +6493,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.9479811363125984</v>
+        <v>0.94499599329788</v>
       </c>
       <c r="E15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -6514,14 +6514,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.9479811363125984</v>
+        <v>0.94499599329788</v>
       </c>
       <c r="E16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -6535,14 +6535,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.94499599329788</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -6556,14 +6556,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.947976644958455</v>
+        <v>0.94499599329788</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -6577,14 +6577,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.947976644958455</v>
+        <v>0.94499599329788</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -6598,11 +6598,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.9474376824612621</v>
+        <v>0.9444554527573394</v>
       </c>
       <c r="E20" t="n">
         <v>19</v>
@@ -6619,11 +6619,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.9474376824612621</v>
+        <v>0.9444554527573394</v>
       </c>
       <c r="E21" t="n">
         <v>19</v>
@@ -6640,14 +6640,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.9474346882251666</v>
+        <v>0.9444554527573394</v>
       </c>
       <c r="E22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -6661,14 +6661,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.9474316939890711</v>
+        <v>0.9444554527573394</v>
       </c>
       <c r="E23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -6682,14 +6682,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.9474316939890711</v>
+        <v>0.9444554527573394</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -6703,14 +6703,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.9474316939890711</v>
+        <v>0.9444539957747505</v>
       </c>
       <c r="E25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -6724,14 +6724,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.9474316939890711</v>
+        <v>0.9444539957747505</v>
       </c>
       <c r="E26" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -6745,14 +6745,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.9444539957747505</v>
       </c>
       <c r="E27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28">
@@ -6766,14 +6766,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.9439192831645661</v>
       </c>
       <c r="E28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -6787,14 +6787,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.9439163691993881</v>
       </c>
       <c r="E29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -6808,14 +6808,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.9439163691993879</v>
       </c>
       <c r="E30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
@@ -6829,14 +6829,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.9439163691993879</v>
       </c>
       <c r="E31" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
@@ -6850,14 +6850,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.943914912216799</v>
       </c>
       <c r="E32" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
@@ -6871,14 +6871,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.943914912216799</v>
       </c>
       <c r="E33" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -6892,14 +6892,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.94391345523421</v>
       </c>
       <c r="E34" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
@@ -6913,14 +6913,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.94391345523421</v>
       </c>
       <c r="E35" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
@@ -6934,14 +6934,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.94391345523421</v>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
@@ -6955,14 +6955,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.94391345523421</v>
       </c>
       <c r="E37" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
@@ -6976,14 +6976,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E38" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
@@ -6997,14 +6997,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E39" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40">
@@ -7018,14 +7018,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E40" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
@@ -7039,14 +7039,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E41" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42">
@@ -7060,14 +7060,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E42" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="43">
@@ -7081,14 +7081,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E43" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44">
@@ -7102,14 +7102,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E44" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="45">
@@ -7123,14 +7123,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E45" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46">
@@ -7144,14 +7144,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E46" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47">
@@ -7165,14 +7165,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E47" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
@@ -7186,14 +7186,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E48" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="49">
@@ -7207,14 +7207,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9439105412690318</v>
       </c>
       <c r="E49" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50">
@@ -7228,14 +7228,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9433758286588476</v>
       </c>
       <c r="E50" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -7249,14 +7249,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.9433758286588475</v>
       </c>
       <c r="E51" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
@@ -7270,14 +7270,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0.9474272026349277</v>
+        <v>0.9433758286588475</v>
       </c>
       <c r="E52" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -7291,14 +7291,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>0.9474272026349277</v>
+        <v>0.9433743716762585</v>
       </c>
       <c r="E53" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="54">
@@ -7312,14 +7312,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.9468852459016392</v>
+        <v>0.9433743716762585</v>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55">
@@ -7333,14 +7333,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.9468852459016392</v>
+        <v>0.9433743716762584</v>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56">
@@ -7354,14 +7354,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.9468837487835916</v>
+        <v>0.9433743716762584</v>
       </c>
       <c r="E56" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57">
@@ -7375,14 +7375,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0.9468837487835916</v>
+        <v>0.9433743716762584</v>
       </c>
       <c r="E57" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58">
@@ -7396,14 +7396,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.9468837487835916</v>
+        <v>0.9433729146936694</v>
       </c>
       <c r="E58" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59">
@@ -7417,14 +7417,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>0.9468837487835916</v>
+        <v>0.9433729146936694</v>
       </c>
       <c r="E59" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60">
@@ -7438,14 +7438,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>0.9468837487835916</v>
+        <v>0.9433729146936694</v>
       </c>
       <c r="E60" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61">
@@ -7459,14 +7459,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.9468792574294482</v>
+        <v>0.9433729146936694</v>
       </c>
       <c r="E61" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62">
@@ -7480,14 +7480,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>0.9468792574294482</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E62" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63">
@@ -7501,14 +7501,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>0.9468792574294482</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E63" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64">
@@ -7522,14 +7522,14 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0.9468792574294482</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E64" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65">
@@ -7543,14 +7543,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.9468792574294482</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E65" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66">
@@ -7564,14 +7564,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>0.9468792574294482</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E66" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67">
@@ -7585,14 +7585,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>0.946343289168351</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E67" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68">
@@ -7606,14 +7606,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>0.946343289168351</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E68" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="69">
@@ -7627,14 +7627,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>0.9463387978142077</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E69" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70">
@@ -7648,14 +7648,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>0.9463387978142077</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E70" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="71">
@@ -7669,14 +7669,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.9463387978142077</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E71" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72">
@@ -7690,14 +7690,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>0.9463387978142077</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E72" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73">
@@ -7711,14 +7711,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>0.94633730069616</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E73" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="74">
@@ -7732,14 +7732,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>0.94633730069616</v>
+        <v>0.9433714577110803</v>
       </c>
       <c r="E74" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75">
@@ -7753,14 +7753,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>0.94633730069616</v>
+        <v>0.9428382020834851</v>
       </c>
       <c r="E75" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76">
@@ -7774,14 +7774,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>0.94633730069616</v>
+        <v>0.9428382020834851</v>
       </c>
       <c r="E76" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77">
@@ -7795,14 +7795,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>0.94633730069616</v>
+        <v>0.9428382020834851</v>
       </c>
       <c r="E77" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="78">
@@ -7816,14 +7816,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>0.94633730069616</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E78" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0.9463373006961598</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E79" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80">
@@ -7858,14 +7858,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>0.9463373006961598</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E80" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81">
@@ -7879,14 +7879,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>0.9463373006961598</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E81" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82">
@@ -7900,14 +7900,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>0.9463373006961598</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E82" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83">
@@ -7921,14 +7921,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>0.9463373006961598</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E83" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84">
@@ -7942,14 +7942,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>0.9463373006961598</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E84" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85">
@@ -7963,14 +7963,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>0.9463358035781122</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E85" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86">
@@ -7984,14 +7984,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>0.9463358035781122</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E86" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87">
@@ -8005,14 +8005,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>0.9463358035781122</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E87" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="88">
@@ -8026,14 +8026,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>0.9463358035781122</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E88" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89">
@@ -8047,14 +8047,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>0.9463358035781122</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E89" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90">
@@ -8068,14 +8068,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.9457908526087282</v>
+        <v>0.9428367451008961</v>
       </c>
       <c r="E90" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91">
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.9457893554906805</v>
+        <v>0.942835288118307</v>
       </c>
       <c r="E91" t="n">
         <v>90</v>
@@ -8110,11 +8110,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.9457893554906805</v>
+        <v>0.942835288118307</v>
       </c>
       <c r="E92" t="n">
         <v>90</v>
@@ -8131,11 +8131,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0.9457893554906805</v>
+        <v>0.942835288118307</v>
       </c>
       <c r="E93" t="n">
         <v>90</v>
@@ -8152,11 +8152,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.9457893554906805</v>
+        <v>0.942835288118307</v>
       </c>
       <c r="E94" t="n">
         <v>90</v>
@@ -8173,11 +8173,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0.9457893554906805</v>
+        <v>0.942835288118307</v>
       </c>
       <c r="E95" t="n">
         <v>90</v>
@@ -8194,11 +8194,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.9457893554906805</v>
+        <v>0.942835288118307</v>
       </c>
       <c r="E96" t="n">
         <v>90</v>
@@ -8215,14 +8215,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>0.9457878583726327</v>
+        <v>0.942835288118307</v>
       </c>
       <c r="E97" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="98">
@@ -8236,14 +8236,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0.9457878583726327</v>
+        <v>0.942835288118307</v>
       </c>
       <c r="E98" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="99">
@@ -8257,14 +8257,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.9457848641365372</v>
+        <v>0.942835288118307</v>
       </c>
       <c r="E99" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="100">
@@ -8278,14 +8278,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.9457848641365372</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E100" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="101">
@@ -8299,14 +8299,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.9457848641365372</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E101" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102">
@@ -8324,10 +8324,10 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.9457848641365372</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E102" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="103">
@@ -8341,11 +8341,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.9452459016393442</v>
+        <v>0.9428323741531288</v>
       </c>
       <c r="E103" t="n">
         <v>102</v>
@@ -8362,11 +8362,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.9452459016393442</v>
+        <v>0.9428323741531288</v>
       </c>
       <c r="E104" t="n">
         <v>102</v>
@@ -8383,14 +8383,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.9452459016393442</v>
+        <v>0.9422976615429446</v>
       </c>
       <c r="E105" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="106">
@@ -8404,11 +8404,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.9452369189310577</v>
+        <v>0.9422976615429445</v>
       </c>
       <c r="E106" t="n">
         <v>105</v>
@@ -8425,11 +8425,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.9452369189310577</v>
+        <v>0.9422976615429445</v>
       </c>
       <c r="E107" t="n">
         <v>105</v>
@@ -8446,14 +8446,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.9452369189310577</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E108" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="109">
@@ -8467,14 +8467,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0.9446979564338648</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E109" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="110">
@@ -8488,14 +8488,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.9446979564338648</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E110" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="111">
@@ -8509,14 +8509,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.9446979564338648</v>
+        <v>0.9422947475777665</v>
       </c>
       <c r="E111" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="112">
@@ -8530,14 +8530,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0.9446979564338648</v>
+        <v>0.9422947475777665</v>
       </c>
       <c r="E112" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="113">
@@ -8551,14 +8551,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.9446979564338648</v>
+        <v>0.9422947475777665</v>
       </c>
       <c r="E113" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="114">
@@ -8572,14 +8572,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.9446979564338648</v>
+        <v>0.9422947475777665</v>
       </c>
       <c r="E114" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="115">
@@ -8593,11 +8593,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>0.9446964593158171</v>
+        <v>0.9422932905951773</v>
       </c>
       <c r="E115" t="n">
         <v>114</v>
@@ -8614,14 +8614,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.9446889737255783</v>
+        <v>0.9422932905951773</v>
       </c>
       <c r="E116" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="117">
@@ -8635,11 +8635,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>0.9441500112283853</v>
+        <v>0.9417585779849931</v>
       </c>
       <c r="E117" t="n">
         <v>116</v>
@@ -8656,11 +8656,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>0.9441500112283853</v>
+        <v>0.9417585779849931</v>
       </c>
       <c r="E118" t="n">
         <v>116</v>
@@ -8677,11 +8677,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>0.9441500112283853</v>
+        <v>0.9417585779849931</v>
       </c>
       <c r="E119" t="n">
         <v>116</v>
@@ -8698,11 +8698,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>0.9441500112283853</v>
+        <v>0.9417585779849931</v>
       </c>
       <c r="E120" t="n">
         <v>116</v>
@@ -8719,14 +8719,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>0.9441500112283853</v>
+        <v>0.9417571210024039</v>
       </c>
       <c r="E121" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122">
@@ -8740,14 +8740,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>0.9441500112283853</v>
+        <v>0.9417571210024039</v>
       </c>
       <c r="E122" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="123">
@@ -8761,14 +8761,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>0.9441455198742421</v>
+        <v>0.9417571210024039</v>
       </c>
       <c r="E123" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="124">
@@ -8782,14 +8782,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>0.9441455198742421</v>
+        <v>0.9417571210024039</v>
       </c>
       <c r="E124" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="125">
@@ -8803,11 +8803,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>0.9436035631409536</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E125" t="n">
         <v>124</v>
@@ -8824,14 +8824,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>0.9436020660229059</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E126" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="127">
@@ -8845,14 +8845,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.9436020660229059</v>
+        <v>0.9417527500546369</v>
       </c>
       <c r="E127" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="128">
@@ -8866,14 +8866,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (100,), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>0.9430571150535221</v>
+        <v>0.9417527500546369</v>
       </c>
       <c r="E128" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="129">
@@ -8887,14 +8887,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>0.9430571150535221</v>
+        <v>0.9412194944270416</v>
       </c>
       <c r="E129" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130">
@@ -8908,14 +8908,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>0.9430571150535221</v>
+        <v>0.9412194944270416</v>
       </c>
       <c r="E130" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="131">
@@ -8929,14 +8929,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>0.9430571150535221</v>
+        <v>0.9412194944270416</v>
       </c>
       <c r="E131" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="132">
@@ -8950,14 +8950,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>0.9430571150535221</v>
+        <v>0.9412180374444524</v>
       </c>
       <c r="E132" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133">
@@ -8971,14 +8971,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>0.9430571150535221</v>
+        <v>0.9412180374444524</v>
       </c>
       <c r="E133" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="134">
@@ -8992,14 +8992,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>0.9430571150535221</v>
+        <v>0.9406847818168572</v>
       </c>
       <c r="E134" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="135">
@@ -9013,14 +9013,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>0.9430571150535221</v>
+        <v>0.9406847818168572</v>
       </c>
       <c r="E135" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136">
@@ -9034,11 +9034,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>0.9425106669660902</v>
+        <v>0.94068041086909</v>
       </c>
       <c r="E136" t="n">
         <v>135</v>
@@ -9055,11 +9055,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>{'activation': 'relu', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.01, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>0.9425106669660902</v>
+        <v>0.94068041086909</v>
       </c>
       <c r="E137" t="n">
         <v>135</v>
@@ -9076,11 +9076,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>0.9425091698480426</v>
+        <v>0.9406789538865009</v>
       </c>
       <c r="E138" t="n">
         <v>137</v>
@@ -9097,14 +9097,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 100}</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>0.9425091698480426</v>
+        <v>0.9401398703285496</v>
       </c>
       <c r="E139" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="140">
@@ -9118,14 +9118,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 500}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>0.9425091698480426</v>
+        <v>0.9401384133459605</v>
       </c>
       <c r="E140" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="141">
@@ -9139,14 +9139,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 1000}</t>
+          <t>{'activation': 'relu', 'alpha': 0.0001, 'hidden_layer_sizes': (30, 20), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>0.9425091698480426</v>
+        <v>0.9401384133459605</v>
       </c>
       <c r="E141" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="142">
@@ -9160,11 +9160,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.0001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>0.9425031813758515</v>
+        <v>0.9396022437531872</v>
       </c>
       <c r="E142" t="n">
         <v>141</v>
@@ -9181,11 +9181,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.001, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.0001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>0.9425031813758515</v>
+        <v>0.9396022437531872</v>
       </c>
       <c r="E143" t="n">
         <v>141</v>
@@ -9202,11 +9202,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.01, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 500}</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>0.9425031813758515</v>
+        <v>0.9396022437531872</v>
       </c>
       <c r="E144" t="n">
         <v>141</v>
@@ -9223,11 +9223,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>{'activation': 'logistic', 'alpha': 0.1, 'hidden_layer_sizes': (20, 10), 'max_iter': 100}</t>
+          <t>{'activation': 'tanh', 'alpha': 0.001, 'hidden_layer_sizes': (50, 50), 'max_iter': 1000}</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>0.9425031813758515</v>
+        <v>0.9396022437531872</v>
       </c>
       <c r="E145" t="n">
         <v>141</v>
@@ -9248,7 +9248,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.9479796391945505</v>
+        <v>0.9455292489254754</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
@@ -9265,11 +9265,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.947976644958455</v>
+        <v>0.944993079332702</v>
       </c>
       <c r="E147" t="n">
         <v>2</v>
@@ -9286,14 +9286,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.9468852459016392</v>
+        <v>0.944993079332702</v>
       </c>
       <c r="E148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -9307,11 +9307,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.9463387978142077</v>
+        <v>0.9433743716762585</v>
       </c>
       <c r="E149" t="n">
         <v>4</v>
@@ -9328,11 +9328,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.9457893554906805</v>
+        <v>0.9433700007284912</v>
       </c>
       <c r="E150" t="n">
         <v>5</v>
@@ -9349,11 +9349,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.9457893554906805</v>
+        <v>0.9433700007284912</v>
       </c>
       <c r="E151" t="n">
         <v>5</v>
@@ -9370,11 +9370,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.9457893554906803</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E152" t="n">
         <v>7</v>
@@ -9391,14 +9391,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 9, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.945786361254585</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E153" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154">
@@ -9412,11 +9412,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.9452444045212965</v>
+        <v>0.9422947475777665</v>
       </c>
       <c r="E154" t="n">
         <v>9</v>
@@ -9433,11 +9433,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.9452444045212965</v>
+        <v>0.9422947475777665</v>
       </c>
       <c r="E155" t="n">
         <v>9</v>
@@ -9454,11 +9454,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>0.9452429074032487</v>
+        <v>0.9422918336125884</v>
       </c>
       <c r="E156" t="n">
         <v>11</v>
@@ -9475,14 +9475,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>0.9452399131671532</v>
+        <v>0.9422918336125884</v>
       </c>
       <c r="E157" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158">
@@ -9496,14 +9496,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>0.9452399131671532</v>
+        <v>0.9417571210024039</v>
       </c>
       <c r="E158" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159">
@@ -9517,14 +9517,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'uniform'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>0.9452399131671532</v>
+        <v>0.9417571210024039</v>
       </c>
       <c r="E159" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160">
@@ -9538,11 +9538,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>0.9446979564338648</v>
+        <v>0.9412180374444524</v>
       </c>
       <c r="E160" t="n">
         <v>15</v>
@@ -9559,11 +9559,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 7, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>0.9446979564338648</v>
+        <v>0.9412180374444524</v>
       </c>
       <c r="E161" t="n">
         <v>15</v>
@@ -9580,14 +9580,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>0.9446979564338648</v>
+        <v>0.9412165804618635</v>
       </c>
       <c r="E162" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="163">
@@ -9601,14 +9601,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.9446979564338648</v>
+        <v>0.9412165804618635</v>
       </c>
       <c r="E163" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="164">
@@ -9622,11 +9622,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>0.9446949621977693</v>
+        <v>0.9412136664966855</v>
       </c>
       <c r="E164" t="n">
         <v>19</v>
@@ -9643,11 +9643,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>0.9446949621977693</v>
+        <v>0.9412136664966855</v>
       </c>
       <c r="E165" t="n">
         <v>19</v>
@@ -9664,14 +9664,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.9446949621977693</v>
+        <v>0.94068041086909</v>
       </c>
       <c r="E166" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="167">
@@ -9685,11 +9685,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.9446934650797216</v>
+        <v>0.9406789538865011</v>
       </c>
       <c r="E167" t="n">
         <v>22</v>
@@ -9706,14 +9706,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 13, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.9446934650797216</v>
+        <v>0.940677496903912</v>
       </c>
       <c r="E168" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="169">
@@ -9727,11 +9727,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.9446919679616738</v>
+        <v>0.9406716689735557</v>
       </c>
       <c r="E169" t="n">
         <v>24</v>
@@ -9748,14 +9748,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 7, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.9446919679616738</v>
+        <v>0.9401398703285496</v>
       </c>
       <c r="E170" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="171">
@@ -9769,11 +9769,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>0.9441455198742421</v>
+        <v>0.9401354993807824</v>
       </c>
       <c r="E171" t="n">
         <v>26</v>
@@ -9790,11 +9790,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 19, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>0.943596077550715</v>
+        <v>0.9401325854156042</v>
       </c>
       <c r="E172" t="n">
         <v>27</v>
@@ -9811,14 +9811,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>0.943596077550715</v>
+        <v>0.9396007867705981</v>
       </c>
       <c r="E173" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="174">
@@ -9832,14 +9832,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>0.9430586121715697</v>
+        <v>0.9396007867705981</v>
       </c>
       <c r="E174" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="175">
@@ -9853,14 +9853,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 11, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 17, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>0.9430586121715697</v>
+        <v>0.93959787280542</v>
       </c>
       <c r="E175" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="176">
@@ -9874,14 +9874,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 17, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>0.9430556179354743</v>
+        <v>0.93959787280542</v>
       </c>
       <c r="E176" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="177">
@@ -9895,14 +9895,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>0.9430556179354743</v>
+        <v>0.9390617032126466</v>
       </c>
       <c r="E177" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="178">
@@ -9916,14 +9916,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>0.9430556179354742</v>
+        <v>0.9390617032126466</v>
       </c>
       <c r="E178" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="179">
@@ -9937,14 +9937,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>0.9430556179354742</v>
+        <v>0.9390617032126466</v>
       </c>
       <c r="E179" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="180">
@@ -9958,14 +9958,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 11, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>0.9430541208174266</v>
+        <v>0.9390617032126466</v>
       </c>
       <c r="E180" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="181">
@@ -9979,14 +9979,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 13, 'weights': 'uniform'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 5, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>0.9430541208174266</v>
+        <v>0.9390617032126466</v>
       </c>
       <c r="E181" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="182">
@@ -10000,14 +10000,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'uniform'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>0.9425076727299947</v>
+        <v>0.9390617032126466</v>
       </c>
       <c r="E182" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="183">
@@ -10021,11 +10021,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>0.9425046784938992</v>
+        <v>0.9385211626721061</v>
       </c>
       <c r="E183" t="n">
         <v>38</v>
@@ -10042,11 +10042,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>0.9425046784938992</v>
+        <v>0.9385211626721061</v>
       </c>
       <c r="E184" t="n">
         <v>38</v>
@@ -10063,14 +10063,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 9, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 9, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>0.9425046784938992</v>
+        <v>0.9379820791141545</v>
       </c>
       <c r="E185" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="186">
@@ -10084,11 +10084,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 17, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>0.9419597275245153</v>
+        <v>0.9379791651489764</v>
       </c>
       <c r="E186" t="n">
         <v>41</v>
@@ -10105,11 +10105,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 19, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>0.941411782319036</v>
+        <v>0.937438624608436</v>
       </c>
       <c r="E187" t="n">
         <v>42</v>
@@ -10126,14 +10126,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 19, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>0.9414102852009881</v>
+        <v>0.937438624608436</v>
       </c>
       <c r="E188" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="189">
@@ -10147,14 +10147,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 9, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'uniform'}</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>0.9414102852009881</v>
+        <v>0.9358272018649376</v>
       </c>
       <c r="E189" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="190">
@@ -10168,11 +10168,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>0.941405793846845</v>
+        <v>0.9352866613243972</v>
       </c>
       <c r="E190" t="n">
         <v>45</v>
@@ -10189,14 +10189,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>0.941405793846845</v>
+        <v>0.9309739928607854</v>
       </c>
       <c r="E191" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="192">
@@ -10210,14 +10210,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'minkowski', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>0.9414057938468448</v>
+        <v>0.9309739928607854</v>
       </c>
       <c r="E192" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="193">
@@ -10231,14 +10231,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>{'metric': 'minkowski', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>0.9414057938468448</v>
+        <v>0.9304349093028339</v>
       </c>
       <c r="E193" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="194">
@@ -10252,11 +10252,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>0.9485245901639345</v>
+        <v>0.9439105412690317</v>
       </c>
       <c r="E194" t="n">
         <v>1</v>
@@ -10273,11 +10273,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>0.9485245901639345</v>
+        <v>0.9439105412690317</v>
       </c>
       <c r="E195" t="n">
         <v>1</v>
@@ -10298,7 +10298,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9433743716762585</v>
       </c>
       <c r="E196" t="n">
         <v>3</v>
@@ -10315,11 +10315,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9433743716762585</v>
       </c>
       <c r="E197" t="n">
         <v>3</v>
@@ -10336,14 +10336,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9433729146936696</v>
       </c>
       <c r="E198" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199">
@@ -10357,14 +10357,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9433729146936696</v>
       </c>
       <c r="E199" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200">
@@ -10378,14 +10378,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9433729146936696</v>
       </c>
       <c r="E200" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201">
@@ -10399,14 +10399,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9433729146936696</v>
       </c>
       <c r="E201" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202">
@@ -10420,14 +10420,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9428323741531288</v>
       </c>
       <c r="E202" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="203">
@@ -10441,14 +10441,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9428323741531288</v>
       </c>
       <c r="E203" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204">
@@ -10462,14 +10462,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9428323741531288</v>
       </c>
       <c r="E204" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="205">
@@ -10483,14 +10483,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E205" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="206">
@@ -10504,14 +10504,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E206" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="207">
@@ -10525,14 +10525,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E207" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="208">
@@ -10546,14 +10546,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E208" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="209">
@@ -10567,14 +10567,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E209" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="210">
@@ -10588,14 +10588,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E210" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="211">
@@ -10609,14 +10609,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E211" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="212">
@@ -10630,14 +10630,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E212" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213">
@@ -10651,14 +10651,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>0.9479781420765028</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E213" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="214">
@@ -10672,14 +10672,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>0.947976644958455</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E214" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="215">
@@ -10693,14 +10693,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>0.947976644958455</v>
+        <v>0.9422962045603555</v>
       </c>
       <c r="E215" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="216">
@@ -10714,14 +10714,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>0.947976644958455</v>
+        <v>0.9422947475777665</v>
       </c>
       <c r="E216" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217">
@@ -10735,14 +10735,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>0.947976644958455</v>
+        <v>0.9422947475777665</v>
       </c>
       <c r="E217" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="218">
@@ -10756,14 +10756,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D218" t="n">
-        <v>0.947976644958455</v>
+        <v>0.9422947475777665</v>
       </c>
       <c r="E218" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="219">
@@ -10777,14 +10777,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>0.947976644958455</v>
+        <v>0.9422947475777665</v>
       </c>
       <c r="E219" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="220">
@@ -10798,11 +10798,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.9422932905951773</v>
       </c>
       <c r="E220" t="n">
         <v>27</v>
@@ -10819,14 +10819,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E221" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="222">
@@ -10840,14 +10840,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(4.281332398719396), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E222" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="223">
@@ -10861,14 +10861,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(11.288378916846883), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E223" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="224">
@@ -10882,14 +10882,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(29.763514416313132), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E224" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="225">
@@ -10903,14 +10903,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D225" t="n">
-        <v>0.9474301968710233</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E225" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="226">
@@ -10924,14 +10924,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(78.47599703514607), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E226" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="227">
@@ -10945,14 +10945,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>0.9474286997529756</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E227" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="228">
@@ -10966,14 +10966,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(206.913808111479), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>0.9474272026349277</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E228" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="229">
@@ -10987,14 +10987,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l1', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0.9468807545474961</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E229" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="230">
@@ -11008,14 +11008,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(545.5594781168514), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>0.9468807545474961</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E230" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="231">
@@ -11029,14 +11029,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>0.9468807545474961</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E231" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="232">
@@ -11050,14 +11050,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1438.44988828766), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>0.9468792574294482</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E232" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="233">
@@ -11071,14 +11071,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.615848211066026), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>0.9468792574294482</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E233" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
     </row>
     <row r="234">
@@ -11092,14 +11092,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(3792.690190732246), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>0.9457848641365372</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E234" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="235">
@@ -11113,14 +11113,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>0.9457848641365372</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E235" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="236">
@@ -11134,14 +11134,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(10000.0), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>0.9457848641365372</v>
+        <v>0.941755664019815</v>
       </c>
       <c r="E236" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="237">
@@ -11155,11 +11155,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>0.9452384160491054</v>
+        <v>0.9417542070372258</v>
       </c>
       <c r="E237" t="n">
         <v>44</v>
@@ -11176,11 +11176,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>0.9452384160491054</v>
+        <v>0.9417542070372258</v>
       </c>
       <c r="E238" t="n">
         <v>44</v>
@@ -11197,11 +11197,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>0.9452384160491054</v>
+        <v>0.9417542070372258</v>
       </c>
       <c r="E239" t="n">
         <v>44</v>
@@ -11218,11 +11218,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>0.9446919679616738</v>
+        <v>0.9417527500546369</v>
       </c>
       <c r="E240" t="n">
         <v>47</v>
@@ -11239,14 +11239,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.23357214690901212), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>0.9446904708436259</v>
+        <v>0.9417527500546369</v>
       </c>
       <c r="E241" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="242">
@@ -11260,11 +11260,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>0.9446889737255783</v>
+        <v>0.9412165804618635</v>
       </c>
       <c r="E242" t="n">
         <v>49</v>
@@ -11281,14 +11281,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0001), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(1.623776739188721), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>0.9419567332884198</v>
+        <v>0.9412165804618635</v>
       </c>
       <c r="E243" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="244">
@@ -11302,14 +11302,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.004832930238571752), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>0.9419567332884198</v>
+        <v>0.9401384133459605</v>
       </c>
       <c r="E244" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="245">
@@ -11323,11 +11323,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'liblinear'}</t>
+          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>0.941955236170372</v>
+        <v>0.9401369563633715</v>
       </c>
       <c r="E245" t="n">
         <v>52</v>
@@ -11344,11 +11344,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0006951927961775605), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.012742749857031334), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>0.9414102852009881</v>
+        <v>0.939599329788009</v>
       </c>
       <c r="E246" t="n">
         <v>53</v>
@@ -11365,11 +11365,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.0018329807108324356), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.08858667904100823), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D247" t="n">
-        <v>0.9408623399955086</v>
+        <v>0.9395935018576527</v>
       </c>
       <c r="E247" t="n">
         <v>54</v>
@@ -11386,11 +11386,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>{'C': np.float64(0.00026366508987303583), 'penalty': 'l2', 'solver': 'lbfgs'}</t>
+          <t>{'C': np.float64(0.03359818286283781), 'penalty': 'l1', 'solver': 'liblinear'}</t>
         </is>
       </c>
       <c r="D248" t="n">
-        <v>0.9299154128303015</v>
+        <v>0.937438624608436</v>
       </c>
       <c r="E248" t="n">
         <v>55</v>
@@ -11411,7 +11411,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>0.8784564712927615</v>
+        <v>0.9358257448823487</v>
       </c>
       <c r="E249" t="n">
         <v>56</v>
@@ -11432,7 +11432,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>0.5000224567707164</v>
+        <v>0.499998543017411</v>
       </c>
       <c r="E250" t="n">
         <v>57</v>
@@ -11453,7 +11453,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>0.5000224567707164</v>
+        <v>0.499998543017411</v>
       </c>
       <c r="E251" t="n">
         <v>57</v>
@@ -11474,7 +11474,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>0.5000224567707164</v>
+        <v>0.499998543017411</v>
       </c>
       <c r="E252" t="n">
         <v>57</v>
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>0.5000224567707164</v>
+        <v>0.499998543017411</v>
       </c>
       <c r="E253" t="n">
         <v>57</v>
@@ -11512,11 +11512,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D254" t="n">
-        <v>0.9485230930458867</v>
+        <v>0.9433729146936696</v>
       </c>
       <c r="E254" t="n">
         <v>1</v>
@@ -11533,11 +11533,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D255" t="n">
-        <v>0.9485230930458867</v>
+        <v>0.9433729146936696</v>
       </c>
       <c r="E255" t="n">
         <v>1</v>
@@ -11554,11 +11554,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'linear'}</t>
+          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D256" t="n">
-        <v>0.9474272026349277</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E256" t="n">
         <v>3</v>
@@ -11575,11 +11575,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'linear'}</t>
+          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D257" t="n">
-        <v>0.9474272026349277</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E257" t="n">
         <v>3</v>
@@ -11596,14 +11596,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'linear'}</t>
+          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D258" t="n">
-        <v>0.9463358035781122</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E258" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259">
@@ -11617,14 +11617,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'linear'}</t>
+          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D259" t="n">
-        <v>0.9463358035781122</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E259" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="260">
@@ -11638,14 +11638,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D260" t="n">
-        <v>0.9457893554906803</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E260" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="261">
@@ -11659,14 +11659,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'linear'}</t>
+          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D261" t="n">
-        <v>0.9457878583726327</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E261" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="262">
@@ -11680,14 +11680,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'linear'}</t>
+          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D262" t="n">
-        <v>0.9457878583726327</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E262" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="263">
@@ -11701,14 +11701,14 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'linear'}</t>
+          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'linear'}</t>
         </is>
       </c>
       <c r="D263" t="n">
-        <v>0.9457878583726327</v>
+        <v>0.9428338311357181</v>
       </c>
       <c r="E263" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="264">
@@ -11722,14 +11722,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'linear'}</t>
+          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D264" t="n">
-        <v>0.9457878583726327</v>
+        <v>0.9428323741531288</v>
       </c>
       <c r="E264" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="265">
@@ -11743,14 +11743,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'linear'}</t>
+          <t>{'C': 1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D265" t="n">
-        <v>0.9457878583726327</v>
+        <v>0.9428323741531288</v>
       </c>
       <c r="E265" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="266">
@@ -11764,14 +11764,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'linear'}</t>
+          <t>{'C': 0.1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D266" t="n">
-        <v>0.9457878583726327</v>
+        <v>0.9428309171705397</v>
       </c>
       <c r="E266" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="267">
@@ -11785,11 +11785,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>{'C': 0.1, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D267" t="n">
-        <v>0.9457848641365372</v>
+        <v>0.9412151234792745</v>
       </c>
       <c r="E267" t="n">
         <v>14</v>
@@ -11806,11 +11806,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D268" t="n">
-        <v>0.9452488958754399</v>
+        <v>0.9412136664966854</v>
       </c>
       <c r="E268" t="n">
         <v>15</v>
@@ -11827,11 +11827,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>{'C': 10, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 100, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D269" t="n">
-        <v>0.944153005464481</v>
+        <v>0.9401354993807823</v>
       </c>
       <c r="E269" t="n">
         <v>16</v>
@@ -11848,11 +11848,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>{'C': 10, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'C': 1, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D270" t="n">
-        <v>0.9441515083464331</v>
+        <v>0.9395964158228309</v>
       </c>
       <c r="E270" t="n">
         <v>17</v>
@@ -11869,11 +11869,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D271" t="n">
-        <v>0.9436005689048581</v>
+        <v>0.9390587892474684</v>
       </c>
       <c r="E271" t="n">
         <v>18</v>
@@ -11890,11 +11890,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'rbf'}</t>
+          <t>{'C': 1000, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D272" t="n">
-        <v>0.9430556179354742</v>
+        <v>0.9385255336198732</v>
       </c>
       <c r="E272" t="n">
         <v>19</v>
@@ -11911,11 +11911,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>{'C': 1000, 'gamma': 'auto', 'kernel': 'rbf'}</t>
+          <t>{'C': 100, 'gamma': 'scale', 'kernel': 'rbf'}</t>
         </is>
       </c>
       <c r="D273" t="n">
-        <v>0.9430526236993787</v>
+        <v>0.9385240766372842</v>
       </c>
       <c r="E273" t="n">
         <v>20</v>
